--- a/docs/Logic Requirements/Ageipelago Joan of Arc.xlsx
+++ b/docs/Logic Requirements/Ageipelago Joan of Arc.xlsx
@@ -8,12 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stefb\OneDrive\Desktop\Logic Requirements\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B2EA931-9906-47E9-82BD-7BDE5EAB488E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03CA79BE-D7FE-4FB0-B3A7-6B86E0F84366}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9E5C4DF5-6A70-45B6-8795-4F3A15A3E9BB}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{9E5C4DF5-6A70-45B6-8795-4F3A15A3E9BB}"/>
   </bookViews>
   <sheets>
     <sheet name="Joan of Arc" sheetId="2" r:id="rId1"/>
+    <sheet name="An unlikely Messiah" sheetId="3" r:id="rId2"/>
+    <sheet name="The Maid of Orleans" sheetId="4" r:id="rId3"/>
+    <sheet name="The Cleansing of the Loire" sheetId="5" r:id="rId4"/>
+    <sheet name="The Rising" sheetId="6" r:id="rId5"/>
+    <sheet name="The Siege of Paris" sheetId="7" r:id="rId6"/>
+    <sheet name="A Perfect Martyr" sheetId="8" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="175">
   <si>
     <t>6 Villagers</t>
   </si>
@@ -1002,90 +1008,6 @@
   <si>
     <r>
       <t xml:space="preserve">Starting Units:
-2 War Galleys
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Moderate:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Later:
-12 Long Swordsmen
-14 Longbowmen
-8 Knights
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Standard:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Later:
-8 Long Swordsmen
-10 Longbowmen
-5 Knights
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Hard:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Later:
-15 Long Swordsmen
-18 Longbowmen
-12 Knights</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Starting Units:
 1 Scout
 </t>
     </r>
@@ -1268,89 +1190,6 @@
     <t>9 Men-at-Arms
 6 Crossbowmen
 1 Scout</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Starting Units:
-6 Spearmen
-2 Scouts
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Moderate:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Later:
-30 Pikemen
-18 Knights
-1 Scout
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Standard:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Later:
-18 Pikemen
-7 Knights
-1 Scout
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Hard:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="14"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Later:
-Identical to Moderate</t>
-    </r>
   </si>
   <si>
     <r>
@@ -3516,12 +3355,460 @@
   <si>
     <t>Due to how powerfull they are, I would recommend turning the 2 Hero Knights in the starting Units into an Item, as they can kill just about everything on the Map when used properly.</t>
   </si>
+  <si>
+    <t>No items required</t>
+  </si>
+  <si>
+    <t>Killable Units</t>
+  </si>
+  <si>
+    <t>Destructible Buildings</t>
+  </si>
+  <si>
+    <t>Deer</t>
+  </si>
+  <si>
+    <t>Grey Wolf</t>
+  </si>
+  <si>
+    <t>Man-at-Arms</t>
+  </si>
+  <si>
+    <t>Spearman</t>
+  </si>
+  <si>
+    <t>Crossbowman</t>
+  </si>
+  <si>
+    <t>Scout Cavalry</t>
+  </si>
+  <si>
+    <t>Archer</t>
+  </si>
+  <si>
+    <t>Light Cavalry</t>
+  </si>
+  <si>
+    <t>Mangonel</t>
+  </si>
+  <si>
+    <t>Coustillier</t>
+  </si>
+  <si>
+    <t>Capped Ram</t>
+  </si>
+  <si>
+    <t>No items required
+Converts to the Player if 'Joan the Maid' approaches them</t>
+  </si>
+  <si>
+    <t>Pikeman</t>
+  </si>
+  <si>
+    <t>War Galley</t>
+  </si>
+  <si>
+    <t>Requires Ranged Units</t>
+  </si>
+  <si>
+    <t>Trebuchet</t>
+  </si>
+  <si>
+    <t>Knight</t>
+  </si>
+  <si>
+    <t>Monk</t>
+  </si>
+  <si>
+    <t>Militia</t>
+  </si>
+  <si>
+    <t>Scorpion</t>
+  </si>
+  <si>
+    <t>Requires Transport Ships
+Converts to the Player if 'Joan the Maid' approaches them</t>
+  </si>
+  <si>
+    <t>Requires Transport Ships</t>
+  </si>
+  <si>
+    <t>Cavalier</t>
+  </si>
+  <si>
+    <t>Onager</t>
+  </si>
+  <si>
+    <t>Elite Longbowman</t>
+  </si>
+  <si>
+    <t>Disappears after Cutscene, but can be killed quickly enough with some effort</t>
+  </si>
+  <si>
+    <t>Palisade Wall</t>
+  </si>
+  <si>
+    <t>Pavilion</t>
+  </si>
+  <si>
+    <t>Pavilion (Large)</t>
+  </si>
+  <si>
+    <t>Archery Range</t>
+  </si>
+  <si>
+    <t>Watch Tower</t>
+  </si>
+  <si>
+    <t>Lumber Camp</t>
+  </si>
+  <si>
+    <t>Mill</t>
+  </si>
+  <si>
+    <t>House</t>
+  </si>
+  <si>
+    <t>Siege Workshop</t>
+  </si>
+  <si>
+    <t>Barracks</t>
+  </si>
+  <si>
+    <t>Stable</t>
+  </si>
+  <si>
+    <t>Monastery</t>
+  </si>
+  <si>
+    <t>Market</t>
+  </si>
+  <si>
+    <t>Dock</t>
+  </si>
+  <si>
+    <t>Outpost</t>
+  </si>
+  <si>
+    <t>Guard Tower</t>
+  </si>
+  <si>
+    <t>Stone Wall</t>
+  </si>
+  <si>
+    <t>Stone Gate</t>
+  </si>
+  <si>
+    <t>Castle</t>
+  </si>
+  <si>
+    <t>Keep</t>
+  </si>
+  <si>
+    <t>Fortified Wall</t>
+  </si>
+  <si>
+    <t>Wild Boar</t>
+  </si>
+  <si>
+    <t>Sheep</t>
+  </si>
+  <si>
+    <t>Villager</t>
+  </si>
+  <si>
+    <t>Long Swordsman</t>
+  </si>
+  <si>
+    <t>Longbowman</t>
+  </si>
+  <si>
+    <t>Battering Ram</t>
+  </si>
+  <si>
+    <t>Field</t>
+  </si>
+  <si>
+    <t>Blacksmith</t>
+  </si>
+  <si>
+    <t>Town Center</t>
+  </si>
+  <si>
+    <t>Mining Camp</t>
+  </si>
+  <si>
+    <t>University</t>
+  </si>
+  <si>
+    <t>Requires Orlèans' Buildings</t>
+  </si>
+  <si>
+    <t>Cathedral</t>
+  </si>
+  <si>
+    <t>If, with the Victory Pavilion, we remove the Defeat Condition after the Objectives are fullfilled, this Building becomes an Option as well.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Starting Units:
+2 War Galleys
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Moderate:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Later:
+12 Long Swordsmen
+14 Longbowmen
+8 Knights
+3 War Galleys
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Standard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Later:
+8 Long Swordsmen
+10 Longbowmen
+5 Knights
+3 War Galleys
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Hard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Later:
+15 Long Swordsmen
+18 Longbowmen
+12 Knights
+3 War Galleys</t>
+    </r>
+  </si>
+  <si>
+    <t>Sir John Fastolf</t>
+  </si>
+  <si>
+    <t>Farm</t>
+  </si>
+  <si>
+    <t>Requires
+-Transport Ships
++ Destroy 1 Castle</t>
+  </si>
+  <si>
+    <t>Dire Wolf</t>
+  </si>
+  <si>
+    <t>Paladin</t>
+  </si>
+  <si>
+    <t>Heavy Scorpion</t>
+  </si>
+  <si>
+    <t>Galleon</t>
+  </si>
+  <si>
+    <t>Cannon Galleon</t>
+  </si>
+  <si>
+    <t>Elite Cannon Galleon</t>
+  </si>
+  <si>
+    <t>Transport Ship</t>
+  </si>
+  <si>
+    <t>Fishing Ship</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Starting Units:
+6 Spearmen
+2 Scouts
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Moderate:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Later:
+30 Pikemen
+18 Knights
+1 Scout
+5 War Galleys
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Standard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Later:
+18 Pikemen
+7 Knights
+1 Scout
+5 War Galleys
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Hard:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Later:
+Identical to Moderate</t>
+    </r>
+  </si>
+  <si>
+    <t>Requires Dock</t>
+  </si>
+  <si>
+    <t>Champion</t>
+  </si>
+  <si>
+    <t>Halberdier</t>
+  </si>
+  <si>
+    <t>No items required
+Only on Hard</t>
+  </si>
+  <si>
+    <t>Fishing Boat</t>
+  </si>
+  <si>
+    <t>Trade Cog</t>
+  </si>
+  <si>
+    <t>No items required
+No Good Way to kill them</t>
+  </si>
+  <si>
+    <t>Elite Coustillier</t>
+  </si>
+  <si>
+    <t>Hussar</t>
+  </si>
+  <si>
+    <t>Siege Ram</t>
+  </si>
+  <si>
+    <t>Trade Workshop</t>
+  </si>
+  <si>
+    <t>Bombard Tower</t>
+  </si>
+  <si>
+    <t>Fortified Gate</t>
+  </si>
+  <si>
+    <t>Bombard Cannon</t>
+  </si>
+  <si>
+    <t>Two-Handed Swordsman</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="32" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3682,16 +3969,70 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFFFF00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFFC000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF7030A0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF00B050"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -3779,11 +4120,59 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3822,6 +4211,105 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4220,23 +4708,23 @@
         <v>15</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>14</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="J4" s="5" t="s">
         <v>36</v>
@@ -4264,23 +4752,23 @@
         <v>13</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>12</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H5" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="I5" s="1" t="s">
         <v>71</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>73</v>
       </c>
       <c r="J5" s="5" t="s">
         <v>41</v>
@@ -4301,25 +4789,25 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="2:17" ht="338.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:17" ht="375.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="12" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>65</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>67</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>9</v>
@@ -4328,17 +4816,17 @@
         <v>43</v>
       </c>
       <c r="K6" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="L6" s="5" t="s">
         <v>44</v>
-      </c>
-      <c r="L6" s="5" t="s">
-        <v>45</v>
       </c>
       <c r="M6" s="5"/>
       <c r="N6" s="5"/>
       <c r="O6" s="5"/>
       <c r="P6" s="5"/>
       <c r="Q6" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="2:17" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
@@ -4346,37 +4834,37 @@
         <v>8</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D7" s="2"/>
       <c r="E7" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>7</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="1"/>
       <c r="J7" s="5" t="s">
-        <v>48</v>
+        <v>159</v>
       </c>
       <c r="K7" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="L7" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="L7" s="5" t="s">
-        <v>51</v>
-      </c>
       <c r="M7" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="N7" s="5"/>
       <c r="O7" s="5"/>
       <c r="P7" s="5"/>
       <c r="Q7" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="2:17" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
@@ -4388,35 +4876,35 @@
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>4</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="L8" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="M8" s="5"/>
       <c r="N8" s="5"/>
       <c r="O8" s="5"/>
       <c r="P8" s="5"/>
       <c r="Q8" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="2:17" ht="409.6" thickBot="1" x14ac:dyDescent="0.3">
@@ -4427,10 +4915,10 @@
         <v>2</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>1</v>
@@ -4439,30 +4927,2594 @@
         <v>0</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="J9" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="K9" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="L9" s="5" t="s">
         <v>56</v>
-      </c>
-      <c r="K9" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="L9" s="5" t="s">
-        <v>58</v>
       </c>
       <c r="M9" s="5"/>
       <c r="N9" s="5"/>
       <c r="O9" s="5"/>
       <c r="P9" s="5"/>
       <c r="Q9" s="5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB235E58-4C38-4EB7-AA36-684DD097C8C8}">
+  <dimension ref="G1:L42"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="7" max="8" width="22.5703125" customWidth="1"/>
+    <col min="11" max="12" width="22.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G2" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G3" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K3" s="43" t="s">
+        <v>112</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G4" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K4" s="25" t="s">
+        <v>113</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G5" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K5" s="44" t="s">
+        <v>114</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G6" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K6" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G7" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K7" s="25" t="s">
+        <v>116</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="8" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G8" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K8" s="25" t="s">
+        <v>117</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="9" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G9" s="41" t="s">
+        <v>92</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K9" s="25" t="s">
+        <v>118</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="10" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G10" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K10" s="25" t="s">
+        <v>119</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="11" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G11" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K11" s="25" t="s">
+        <v>120</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="12" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G12" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K12" s="25" t="s">
+        <v>121</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="13" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G13" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K13" s="25" t="s">
+        <v>122</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="14" spans="7:12" ht="112.5" x14ac:dyDescent="0.25">
+      <c r="G14" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="K14" s="25" t="s">
+        <v>123</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="15" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G15" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="K15" s="25" t="s">
+        <v>124</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="16" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G16" s="20" t="s">
+        <v>101</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="K16" s="25" t="s">
+        <v>125</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="17" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G17" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="K17" s="26" t="s">
+        <v>126</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="18" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G18" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="K18" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="19" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G19" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="K19" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="20" spans="7:12" ht="131.25" x14ac:dyDescent="0.25">
+      <c r="G20" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="K20" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="21" spans="7:12" ht="93.75" x14ac:dyDescent="0.25">
+      <c r="G21" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="K21" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="22" spans="7:12" ht="93.75" x14ac:dyDescent="0.25">
+      <c r="G22" s="23" t="s">
+        <v>109</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="K22" s="27" t="s">
+        <v>131</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="23" spans="7:12" ht="93.75" x14ac:dyDescent="0.25">
+      <c r="G23" s="23" t="s">
+        <v>110</v>
+      </c>
+      <c r="H23" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="K23" s="27" t="s">
+        <v>132</v>
+      </c>
+      <c r="L23" s="14" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G24" s="15"/>
+      <c r="H24" s="15"/>
+      <c r="K24" s="15"/>
+      <c r="L24" s="15"/>
+    </row>
+    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G25" s="24"/>
+      <c r="H25" s="24"/>
+      <c r="K25" s="24"/>
+      <c r="L25" s="24"/>
+    </row>
+    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G26" s="24"/>
+      <c r="H26" s="24"/>
+      <c r="K26" s="24"/>
+      <c r="L26" s="24"/>
+    </row>
+    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G27" s="24"/>
+      <c r="H27" s="24"/>
+      <c r="K27" s="24"/>
+      <c r="L27" s="24"/>
+    </row>
+    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G28" s="24"/>
+      <c r="H28" s="24"/>
+      <c r="K28" s="24"/>
+      <c r="L28" s="24"/>
+    </row>
+    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G29" s="24"/>
+      <c r="H29" s="24"/>
+      <c r="K29" s="24"/>
+      <c r="L29" s="24"/>
+    </row>
+    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G30" s="24"/>
+      <c r="H30" s="24"/>
+      <c r="K30" s="24"/>
+      <c r="L30" s="24"/>
+    </row>
+    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G31" s="24"/>
+      <c r="H31" s="24"/>
+      <c r="K31" s="24"/>
+      <c r="L31" s="24"/>
+    </row>
+    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G32" s="24"/>
+      <c r="H32" s="24"/>
+      <c r="K32" s="24"/>
+      <c r="L32" s="24"/>
+    </row>
+    <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G33" s="16"/>
+      <c r="H33" s="16"/>
+      <c r="K33" s="16"/>
+      <c r="L33" s="16"/>
+    </row>
+    <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G34" s="16"/>
+      <c r="H34" s="16"/>
+      <c r="K34" s="16"/>
+      <c r="L34" s="16"/>
+    </row>
+    <row r="35" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G35" s="16"/>
+      <c r="H35" s="16"/>
+      <c r="K35" s="16"/>
+      <c r="L35" s="16"/>
+    </row>
+    <row r="36" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G36" s="16"/>
+      <c r="H36" s="16"/>
+      <c r="K36" s="16"/>
+      <c r="L36" s="16"/>
+    </row>
+    <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G37" s="16"/>
+      <c r="H37" s="16"/>
+      <c r="K37" s="16"/>
+      <c r="L37" s="16"/>
+    </row>
+    <row r="38" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G38" s="16"/>
+      <c r="H38" s="16"/>
+      <c r="K38" s="16"/>
+      <c r="L38" s="16"/>
+    </row>
+    <row r="39" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G39" s="16"/>
+      <c r="H39" s="16"/>
+      <c r="K39" s="16"/>
+      <c r="L39" s="16"/>
+    </row>
+    <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G40" s="16"/>
+      <c r="H40" s="16"/>
+      <c r="K40" s="16"/>
+      <c r="L40" s="16"/>
+    </row>
+    <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G41" s="16"/>
+      <c r="H41" s="16"/>
+      <c r="K41" s="16"/>
+      <c r="L41" s="16"/>
+    </row>
+    <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G42" s="16"/>
+      <c r="H42" s="16"/>
+      <c r="K42" s="16"/>
+      <c r="L42" s="16"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54428EA1-B8FA-4CDC-9D60-36F1167331A2}">
+  <dimension ref="G1:L42"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="7" max="8" width="22.5703125" customWidth="1"/>
+    <col min="11" max="12" width="22.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G2" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G3" s="38" t="s">
+        <v>133</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K3" s="29" t="s">
+        <v>119</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G4" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K4" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G5" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K5" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G6" s="28" t="s">
+        <v>135</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K6" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G7" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K7" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="8" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G8" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K8" s="28" t="s">
+        <v>139</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="9" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G9" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K9" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="10" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G10" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K10" s="28" t="s">
+        <v>124</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="11" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G11" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K11" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="12" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G12" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K12" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="13" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G13" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K13" s="28" t="s">
+        <v>130</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="14" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G14" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K14" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="15" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G15" s="22" t="s">
+        <v>137</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K15" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="16" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G16" s="22" t="s">
+        <v>94</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K16" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G17" s="27" t="s">
+        <v>138</v>
+      </c>
+      <c r="H17" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="K17" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G18" s="15"/>
+      <c r="H18" s="15"/>
+      <c r="K18" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="19" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G19" s="24"/>
+      <c r="H19" s="24"/>
+      <c r="K19" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="20" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G20" s="24"/>
+      <c r="H20" s="24"/>
+      <c r="K20" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="21" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G21" s="24"/>
+      <c r="H21" s="24"/>
+      <c r="K21" s="23" t="s">
+        <v>126</v>
+      </c>
+      <c r="L21" s="14" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="22" spans="7:12" ht="150" x14ac:dyDescent="0.25">
+      <c r="G22" s="24"/>
+      <c r="H22" s="24"/>
+      <c r="K22" s="30" t="s">
+        <v>145</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G23" s="24"/>
+      <c r="H23" s="24"/>
+      <c r="K23" s="24"/>
+      <c r="L23" s="24"/>
+    </row>
+    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G24" s="24"/>
+      <c r="H24" s="24"/>
+      <c r="K24" s="24"/>
+      <c r="L24" s="24"/>
+    </row>
+    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G25" s="24"/>
+      <c r="H25" s="24"/>
+      <c r="K25" s="24"/>
+      <c r="L25" s="24"/>
+    </row>
+    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G26" s="24"/>
+      <c r="H26" s="24"/>
+      <c r="K26" s="24"/>
+      <c r="L26" s="24"/>
+    </row>
+    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G27" s="24"/>
+      <c r="H27" s="24"/>
+      <c r="K27" s="24"/>
+      <c r="L27" s="24"/>
+    </row>
+    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G28" s="24"/>
+      <c r="H28" s="24"/>
+      <c r="K28" s="24"/>
+      <c r="L28" s="24"/>
+    </row>
+    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G29" s="24"/>
+      <c r="H29" s="24"/>
+      <c r="K29" s="24"/>
+      <c r="L29" s="24"/>
+    </row>
+    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G30" s="24"/>
+      <c r="H30" s="24"/>
+      <c r="K30" s="24"/>
+      <c r="L30" s="24"/>
+    </row>
+    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G31" s="24"/>
+      <c r="H31" s="24"/>
+      <c r="K31" s="24"/>
+      <c r="L31" s="24"/>
+    </row>
+    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G32" s="24"/>
+      <c r="H32" s="24"/>
+      <c r="K32" s="24"/>
+      <c r="L32" s="24"/>
+    </row>
+    <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G33" s="16"/>
+      <c r="H33" s="16"/>
+      <c r="K33" s="16"/>
+      <c r="L33" s="16"/>
+    </row>
+    <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G34" s="16"/>
+      <c r="H34" s="16"/>
+      <c r="K34" s="16"/>
+      <c r="L34" s="16"/>
+    </row>
+    <row r="35" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G35" s="16"/>
+      <c r="H35" s="16"/>
+      <c r="K35" s="16"/>
+      <c r="L35" s="16"/>
+    </row>
+    <row r="36" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G36" s="16"/>
+      <c r="H36" s="16"/>
+      <c r="K36" s="16"/>
+      <c r="L36" s="16"/>
+    </row>
+    <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G37" s="16"/>
+      <c r="H37" s="16"/>
+      <c r="K37" s="16"/>
+      <c r="L37" s="16"/>
+    </row>
+    <row r="38" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G38" s="16"/>
+      <c r="H38" s="16"/>
+      <c r="K38" s="16"/>
+      <c r="L38" s="16"/>
+    </row>
+    <row r="39" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G39" s="16"/>
+      <c r="H39" s="16"/>
+      <c r="K39" s="16"/>
+      <c r="L39" s="16"/>
+    </row>
+    <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G40" s="16"/>
+      <c r="H40" s="16"/>
+      <c r="K40" s="16"/>
+      <c r="L40" s="16"/>
+    </row>
+    <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G41" s="16"/>
+      <c r="H41" s="16"/>
+      <c r="K41" s="16"/>
+      <c r="L41" s="16"/>
+    </row>
+    <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G42" s="16"/>
+      <c r="H42" s="16"/>
+      <c r="K42" s="16"/>
+      <c r="L42" s="16"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EA9158E-5B25-4659-9455-CB16792B33F3}">
+  <dimension ref="G1:L42"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="7" max="8" width="22.5703125" customWidth="1"/>
+    <col min="11" max="12" width="22.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G2" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G3" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="K3" s="32" t="s">
+        <v>119</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="4" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G4" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="K4" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="5" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G5" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="K5" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="6" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G6" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="K6" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="7" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G7" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="K7" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="8" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G8" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="K8" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="9" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G9" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="K9" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="10" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G10" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="K10" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="11" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G11" s="22" t="s">
+        <v>137</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="K11" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="12" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G12" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="K12" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="13" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G13" s="22" t="s">
+        <v>99</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="K13" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="14" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G14" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="K14" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="15" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G15" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="K15" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="16" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G16" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="K16" s="22" t="s">
+        <v>115</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="17" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G17" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="K17" s="22" t="s">
+        <v>122</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="18" spans="7:12" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="G18" s="31" t="s">
+        <v>148</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="K18" s="22" t="s">
+        <v>125</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="19" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G19" s="15"/>
+      <c r="H19" s="15"/>
+      <c r="K19" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="20" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G20" s="24"/>
+      <c r="H20" s="24"/>
+      <c r="K20" s="22" t="s">
+        <v>126</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="21" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G21" s="24"/>
+      <c r="H21" s="24"/>
+      <c r="K21" s="22" t="s">
+        <v>143</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="22" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G22" s="24"/>
+      <c r="H22" s="24"/>
+      <c r="K22" s="45" t="s">
+        <v>116</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G23" s="24"/>
+      <c r="H23" s="24"/>
+      <c r="K23" s="15"/>
+      <c r="L23" s="15"/>
+    </row>
+    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G24" s="24"/>
+      <c r="H24" s="24"/>
+      <c r="K24" s="24"/>
+      <c r="L24" s="24"/>
+    </row>
+    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G25" s="24"/>
+      <c r="H25" s="24"/>
+      <c r="K25" s="24"/>
+      <c r="L25" s="24"/>
+    </row>
+    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G26" s="24"/>
+      <c r="H26" s="24"/>
+      <c r="K26" s="24"/>
+      <c r="L26" s="24"/>
+    </row>
+    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G27" s="24"/>
+      <c r="H27" s="24"/>
+      <c r="K27" s="24"/>
+      <c r="L27" s="24"/>
+    </row>
+    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G28" s="24"/>
+      <c r="H28" s="24"/>
+      <c r="K28" s="24"/>
+      <c r="L28" s="24"/>
+    </row>
+    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G29" s="24"/>
+      <c r="H29" s="24"/>
+      <c r="K29" s="24"/>
+      <c r="L29" s="24"/>
+    </row>
+    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G30" s="24"/>
+      <c r="H30" s="24"/>
+      <c r="K30" s="24"/>
+      <c r="L30" s="24"/>
+    </row>
+    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G31" s="24"/>
+      <c r="H31" s="24"/>
+      <c r="K31" s="24"/>
+      <c r="L31" s="24"/>
+    </row>
+    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G32" s="24"/>
+      <c r="H32" s="24"/>
+      <c r="K32" s="24"/>
+      <c r="L32" s="24"/>
+    </row>
+    <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G33" s="16"/>
+      <c r="H33" s="16"/>
+      <c r="K33" s="16"/>
+      <c r="L33" s="16"/>
+    </row>
+    <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G34" s="16"/>
+      <c r="H34" s="16"/>
+      <c r="K34" s="16"/>
+      <c r="L34" s="16"/>
+    </row>
+    <row r="35" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G35" s="16"/>
+      <c r="H35" s="16"/>
+      <c r="K35" s="16"/>
+      <c r="L35" s="16"/>
+    </row>
+    <row r="36" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G36" s="16"/>
+      <c r="H36" s="16"/>
+      <c r="K36" s="16"/>
+      <c r="L36" s="16"/>
+    </row>
+    <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G37" s="16"/>
+      <c r="H37" s="16"/>
+      <c r="K37" s="16"/>
+      <c r="L37" s="16"/>
+    </row>
+    <row r="38" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G38" s="16"/>
+      <c r="H38" s="16"/>
+      <c r="K38" s="16"/>
+      <c r="L38" s="16"/>
+    </row>
+    <row r="39" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G39" s="16"/>
+      <c r="H39" s="16"/>
+      <c r="K39" s="16"/>
+      <c r="L39" s="16"/>
+    </row>
+    <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G40" s="16"/>
+      <c r="H40" s="16"/>
+      <c r="K40" s="16"/>
+      <c r="L40" s="16"/>
+    </row>
+    <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G41" s="16"/>
+      <c r="H41" s="16"/>
+      <c r="K41" s="16"/>
+      <c r="L41" s="16"/>
+    </row>
+    <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G42" s="16"/>
+      <c r="H42" s="16"/>
+      <c r="K42" s="16"/>
+      <c r="L42" s="16"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8F06796-6B63-4D23-8399-5C2D3A86CDB8}">
+  <dimension ref="G1:L42"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="7" max="8" width="22.5703125" customWidth="1"/>
+    <col min="11" max="12" width="22.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G2" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G3" s="34" t="s">
+        <v>134</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K3" s="33" t="s">
+        <v>113</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G4" s="40" t="s">
+        <v>151</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K4" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G5" s="35" t="s">
+        <v>91</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K5" s="26" t="s">
+        <v>119</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G6" s="22" t="s">
+        <v>88</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K6" s="26" t="s">
+        <v>125</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G7" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K7" s="26" t="s">
+        <v>143</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="8" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G8" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K8" s="26" t="s">
+        <v>117</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="9" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G9" s="26" t="s">
+        <v>102</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K9" s="26" t="s">
+        <v>140</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="10" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G10" s="42" t="s">
+        <v>105</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K10" s="26" t="s">
+        <v>122</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="11" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G11" s="26" t="s">
+        <v>138</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K11" s="26" t="s">
+        <v>118</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="12" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G12" s="26" t="s">
+        <v>108</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K12" s="26" t="s">
+        <v>149</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="13" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G13" s="26" t="s">
+        <v>152</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K13" s="26" t="s">
+        <v>120</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="14" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G14" s="42" t="s">
+        <v>153</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K14" s="26" t="s">
+        <v>142</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="15" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G15" s="26" t="s">
+        <v>96</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K15" s="26" t="s">
+        <v>121</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="16" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G16" s="26" t="s">
+        <v>99</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K16" s="26" t="s">
+        <v>124</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G17" s="26" t="s">
+        <v>154</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K17" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G18" s="26" t="s">
+        <v>155</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K18" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="19" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G19" s="42" t="s">
+        <v>156</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K19" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G20" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K20" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G21" s="20" t="s">
+        <v>98</v>
+      </c>
+      <c r="H21" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="K21" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G22" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K22" s="36" t="s">
+        <v>145</v>
+      </c>
+      <c r="L22" s="14" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G23" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K23" s="15"/>
+      <c r="L23" s="15"/>
+    </row>
+    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G24" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K24" s="24"/>
+      <c r="L24" s="24"/>
+    </row>
+    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G25" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K25" s="24"/>
+      <c r="L25" s="24"/>
+    </row>
+    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G26" s="36" t="s">
+        <v>109</v>
+      </c>
+      <c r="H26" s="14" t="s">
+        <v>83</v>
+      </c>
+      <c r="K26" s="24"/>
+      <c r="L26" s="24"/>
+    </row>
+    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G27" s="20" t="s">
+        <v>158</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="K27" s="24"/>
+      <c r="L27" s="24"/>
+    </row>
+    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G28" s="42" t="s">
+        <v>157</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="K28" s="24"/>
+      <c r="L28" s="24"/>
+    </row>
+    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="K29" s="24"/>
+      <c r="L29" s="24"/>
+    </row>
+    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G30" s="24"/>
+      <c r="H30" s="24"/>
+      <c r="K30" s="24"/>
+      <c r="L30" s="24"/>
+    </row>
+    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G31" s="24"/>
+      <c r="H31" s="24"/>
+      <c r="K31" s="24"/>
+      <c r="L31" s="24"/>
+    </row>
+    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G32" s="24"/>
+      <c r="H32" s="24"/>
+      <c r="K32" s="24"/>
+      <c r="L32" s="24"/>
+    </row>
+    <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G33" s="16"/>
+      <c r="H33" s="16"/>
+      <c r="K33" s="16"/>
+      <c r="L33" s="16"/>
+    </row>
+    <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G34" s="16"/>
+      <c r="H34" s="16"/>
+      <c r="K34" s="16"/>
+      <c r="L34" s="16"/>
+    </row>
+    <row r="35" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G35" s="16"/>
+      <c r="H35" s="16"/>
+      <c r="K35" s="16"/>
+      <c r="L35" s="16"/>
+    </row>
+    <row r="36" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G36" s="16"/>
+      <c r="H36" s="16"/>
+      <c r="K36" s="16"/>
+      <c r="L36" s="16"/>
+    </row>
+    <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G37" s="16"/>
+      <c r="H37" s="16"/>
+      <c r="K37" s="16"/>
+      <c r="L37" s="16"/>
+    </row>
+    <row r="38" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G38" s="16"/>
+      <c r="H38" s="16"/>
+      <c r="K38" s="16"/>
+      <c r="L38" s="16"/>
+    </row>
+    <row r="39" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G39" s="16"/>
+      <c r="H39" s="16"/>
+      <c r="K39" s="16"/>
+      <c r="L39" s="16"/>
+    </row>
+    <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G40" s="16"/>
+      <c r="H40" s="16"/>
+      <c r="K40" s="16"/>
+      <c r="L40" s="16"/>
+    </row>
+    <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G41" s="16"/>
+      <c r="H41" s="16"/>
+      <c r="K41" s="16"/>
+      <c r="L41" s="16"/>
+    </row>
+    <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G42" s="16"/>
+      <c r="H42" s="16"/>
+      <c r="K42" s="16"/>
+      <c r="L42" s="16"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66C252C5-A4A0-46E4-AF3D-69F9DB4F2D8C}">
+  <dimension ref="G1:L42"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="7" max="8" width="22.5703125" customWidth="1"/>
+    <col min="11" max="12" width="22.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G2" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G3" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K3" s="33" t="s">
+        <v>119</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G4" s="35" t="s">
+        <v>135</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K4" s="22" t="s">
+        <v>118</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G5" s="35" t="s">
+        <v>161</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K5" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G6" s="22" t="s">
+        <v>162</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K6" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G7" s="22" t="s">
+        <v>110</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K7" s="46" t="s">
+        <v>170</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="8" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G8" s="22" t="s">
+        <v>108</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K8" s="22" t="s">
+        <v>171</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="9" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G9" s="22" t="s">
+        <v>101</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K9" s="22" t="s">
+        <v>131</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="10" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G10" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K10" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="11" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G11" s="22" t="s">
+        <v>155</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K11" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="12" spans="7:12" ht="56.25" x14ac:dyDescent="0.25">
+      <c r="G12" s="22" t="s">
+        <v>103</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="K12" s="22" t="s">
+        <v>172</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="13" spans="7:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="G13" s="22" t="s">
+        <v>164</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="K13" s="22" t="s">
+        <v>117</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="14" spans="7:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="G14" s="22" t="s">
+        <v>165</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="K14" s="22" t="s">
+        <v>140</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="15" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G15" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K15" s="22" t="s">
+        <v>125</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="16" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G16" s="41" t="s">
+        <v>167</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K16" s="22" t="s">
+        <v>124</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G17" s="41" t="s">
+        <v>168</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K17" s="22" t="s">
+        <v>141</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G18" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K18" s="22" t="s">
+        <v>121</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G19" s="41" t="s">
+        <v>169</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K19" s="22" t="s">
+        <v>122</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G20" s="28" t="s">
+        <v>90</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K20" s="22" t="s">
+        <v>115</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="21" spans="7:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="G21" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="K21" s="22" t="s">
+        <v>120</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G22" s="24"/>
+      <c r="H22" s="24"/>
+      <c r="K22" s="23" t="s">
+        <v>145</v>
+      </c>
+      <c r="L22" s="14" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G23" s="24"/>
+      <c r="H23" s="24"/>
+      <c r="K23" s="15"/>
+      <c r="L23" s="15"/>
+    </row>
+    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G24" s="24"/>
+      <c r="H24" s="24"/>
+      <c r="K24" s="24"/>
+      <c r="L24" s="24"/>
+    </row>
+    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G25" s="24"/>
+      <c r="H25" s="24"/>
+      <c r="K25" s="24"/>
+      <c r="L25" s="24"/>
+    </row>
+    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G26" s="24"/>
+      <c r="H26" s="24"/>
+      <c r="K26" s="24"/>
+      <c r="L26" s="24"/>
+    </row>
+    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G27" s="24"/>
+      <c r="H27" s="24"/>
+      <c r="K27" s="24"/>
+      <c r="L27" s="24"/>
+    </row>
+    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G28" s="24"/>
+      <c r="H28" s="24"/>
+      <c r="K28" s="24"/>
+      <c r="L28" s="24"/>
+    </row>
+    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G29" s="24"/>
+      <c r="H29" s="24"/>
+      <c r="K29" s="24"/>
+      <c r="L29" s="24"/>
+    </row>
+    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G30" s="24"/>
+      <c r="H30" s="24"/>
+      <c r="K30" s="24"/>
+      <c r="L30" s="24"/>
+    </row>
+    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G31" s="24"/>
+      <c r="H31" s="24"/>
+      <c r="K31" s="24"/>
+      <c r="L31" s="24"/>
+    </row>
+    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G32" s="24"/>
+      <c r="H32" s="24"/>
+      <c r="K32" s="24"/>
+      <c r="L32" s="24"/>
+    </row>
+    <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G33" s="16"/>
+      <c r="H33" s="16"/>
+      <c r="K33" s="16"/>
+      <c r="L33" s="16"/>
+    </row>
+    <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G34" s="16"/>
+      <c r="H34" s="16"/>
+      <c r="K34" s="16"/>
+      <c r="L34" s="16"/>
+    </row>
+    <row r="35" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G35" s="16"/>
+      <c r="H35" s="16"/>
+      <c r="K35" s="16"/>
+      <c r="L35" s="16"/>
+    </row>
+    <row r="36" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G36" s="16"/>
+      <c r="H36" s="16"/>
+      <c r="K36" s="16"/>
+      <c r="L36" s="16"/>
+    </row>
+    <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G37" s="16"/>
+      <c r="H37" s="16"/>
+      <c r="K37" s="16"/>
+      <c r="L37" s="16"/>
+    </row>
+    <row r="38" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G38" s="16"/>
+      <c r="H38" s="16"/>
+      <c r="K38" s="16"/>
+      <c r="L38" s="16"/>
+    </row>
+    <row r="39" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G39" s="16"/>
+      <c r="H39" s="16"/>
+      <c r="K39" s="16"/>
+      <c r="L39" s="16"/>
+    </row>
+    <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G40" s="16"/>
+      <c r="H40" s="16"/>
+      <c r="K40" s="16"/>
+      <c r="L40" s="16"/>
+    </row>
+    <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G41" s="16"/>
+      <c r="H41" s="16"/>
+      <c r="K41" s="16"/>
+      <c r="L41" s="16"/>
+    </row>
+    <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G42" s="16"/>
+      <c r="H42" s="16"/>
+      <c r="K42" s="16"/>
+      <c r="L42" s="16"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84FA3A52-228B-4A13-B0AF-579CAC1203E1}">
+  <dimension ref="G1:L42"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="7" max="8" width="22.5703125" customWidth="1"/>
+    <col min="11" max="12" width="22.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="7:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="7:12" ht="47.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="G2" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G3" s="32" t="s">
+        <v>135</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K3" s="32" t="s">
+        <v>132</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G4" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K4" s="39" t="s">
+        <v>172</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G5" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K5" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G6" s="19" t="s">
+        <v>93</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K6" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="7" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G7" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K7" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="8" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G8" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K8" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="9" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G9" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K9" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="10" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G10" s="19" t="s">
+        <v>173</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K10" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="11" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G11" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K11" s="19" t="s">
+        <v>118</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="12" spans="7:12" ht="37.5" x14ac:dyDescent="0.25">
+      <c r="G12" s="41" t="s">
+        <v>174</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K12" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="13" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G13" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K13" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="14" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G14" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K14" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="15" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G15" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K15" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="16" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G16" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K16" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="17" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G17" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K17" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="18" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G18" s="22" t="s">
+        <v>137</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K18" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="19" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G19" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K19" s="22" t="s">
+        <v>171</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="20" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G20" s="22" t="s">
+        <v>155</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K20" s="22" t="s">
+        <v>120</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="21" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G21" s="22" t="s">
+        <v>110</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="K21" s="22" t="s">
+        <v>122</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="22" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G22" s="37" t="s">
+        <v>164</v>
+      </c>
+      <c r="H22" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="K22" s="23" t="s">
+        <v>143</v>
+      </c>
+      <c r="L22" s="14" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="23" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G23" s="15"/>
+      <c r="H23" s="15"/>
+      <c r="K23" s="15"/>
+      <c r="L23" s="15"/>
+    </row>
+    <row r="24" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G24" s="24"/>
+      <c r="H24" s="24"/>
+      <c r="K24" s="24"/>
+      <c r="L24" s="24"/>
+    </row>
+    <row r="25" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G25" s="24"/>
+      <c r="H25" s="24"/>
+      <c r="K25" s="24"/>
+      <c r="L25" s="24"/>
+    </row>
+    <row r="26" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G26" s="24"/>
+      <c r="H26" s="24"/>
+      <c r="K26" s="24"/>
+      <c r="L26" s="24"/>
+    </row>
+    <row r="27" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G27" s="24"/>
+      <c r="H27" s="24"/>
+      <c r="K27" s="24"/>
+      <c r="L27" s="24"/>
+    </row>
+    <row r="28" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G28" s="24"/>
+      <c r="H28" s="24"/>
+      <c r="K28" s="24"/>
+      <c r="L28" s="24"/>
+    </row>
+    <row r="29" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G29" s="24"/>
+      <c r="H29" s="24"/>
+      <c r="K29" s="24"/>
+      <c r="L29" s="24"/>
+    </row>
+    <row r="30" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G30" s="24"/>
+      <c r="H30" s="24"/>
+      <c r="K30" s="24"/>
+      <c r="L30" s="24"/>
+    </row>
+    <row r="31" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G31" s="24"/>
+      <c r="H31" s="24"/>
+      <c r="K31" s="24"/>
+      <c r="L31" s="24"/>
+    </row>
+    <row r="32" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G32" s="24"/>
+      <c r="H32" s="24"/>
+      <c r="K32" s="24"/>
+      <c r="L32" s="24"/>
+    </row>
+    <row r="33" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G33" s="16"/>
+      <c r="H33" s="16"/>
+      <c r="K33" s="16"/>
+      <c r="L33" s="16"/>
+    </row>
+    <row r="34" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G34" s="16"/>
+      <c r="H34" s="16"/>
+      <c r="K34" s="16"/>
+      <c r="L34" s="16"/>
+    </row>
+    <row r="35" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G35" s="16"/>
+      <c r="H35" s="16"/>
+      <c r="K35" s="16"/>
+      <c r="L35" s="16"/>
+    </row>
+    <row r="36" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G36" s="16"/>
+      <c r="H36" s="16"/>
+      <c r="K36" s="16"/>
+      <c r="L36" s="16"/>
+    </row>
+    <row r="37" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G37" s="16"/>
+      <c r="H37" s="16"/>
+      <c r="K37" s="16"/>
+      <c r="L37" s="16"/>
+    </row>
+    <row r="38" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G38" s="16"/>
+      <c r="H38" s="16"/>
+      <c r="K38" s="16"/>
+      <c r="L38" s="16"/>
+    </row>
+    <row r="39" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G39" s="16"/>
+      <c r="H39" s="16"/>
+      <c r="K39" s="16"/>
+      <c r="L39" s="16"/>
+    </row>
+    <row r="40" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G40" s="16"/>
+      <c r="H40" s="16"/>
+      <c r="K40" s="16"/>
+      <c r="L40" s="16"/>
+    </row>
+    <row r="41" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G41" s="16"/>
+      <c r="H41" s="16"/>
+      <c r="K41" s="16"/>
+      <c r="L41" s="16"/>
+    </row>
+    <row r="42" spans="7:12" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="G42" s="16"/>
+      <c r="H42" s="16"/>
+      <c r="K42" s="16"/>
+      <c r="L42" s="16"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
 </file>